--- a/HistoricoDoMeuExperimento.xlsx
+++ b/HistoricoDoMeuExperimento.xlsx
@@ -16,9 +16,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
   <si>
-    <t>Model Name and Version - Agent Name - Skills and Agents</t>
+    <r>
+      <rPr>
+        <rFont val="Helvetica Neue"/>
+        <color rgb="FF000000"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">claude-4.6-sonnet-medium - Cursor - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Helvetica Neue"/>
+        <color rgb="FF1155CC"/>
+        <sz val="12.0"/>
+        <u/>
+      </rPr>
+      <t>AGENTS.md</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Helvetica Neue"/>
+        <color rgb="FF000000"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve"> (design-feature, implement-feature, refactor-for-clarity, review-code, write-tests)</t>
+    </r>
   </si>
   <si>
     <t>Prompt</t>
@@ -36,14 +60,907 @@
     <t>Observations</t>
   </si>
   <si>
-    <t>c</t>
+    <t>@AGENTS.md 
+I want to plan the development of a web-based system for exam creation and grading.
+The system must strictly follow these requirements:
+1. Question Management
+- The system must allow creating, updating, deleting, and listing closed questions
+- Each question has:
+  - a statement
+  - a set of alternatives
+- Each alternative has:
+  - a description
+  - a boolean indicating whether it is correct
+- The user must be able to add, update, and remove alternatives within a question
+2. Exam Management
+- The system must allow creating, updating, and deleting exams
+- Each exam is composed of a selection of previously created questions
+- The user must define how answers are represented:
+  - either by letters (A, B, C...)
+  - or by powers of 2 (1, 2, 4, 8, ...)
+- For letters:
+  - the exam must include space for marking selected letters
+- For powers of 2:
+  - the exam must include space for writing the sum of selected alternatives
+3. Exam Generation
+- The system must generate multiple versions of an exam
+- Each generated exam must:
+  - randomize the order of questions
+  - randomize the order of alternatives
+- The system must generate:
+  - a PDF for each exam version
+  - a CSV file with the answer key
+- Each PDF must include:
+  - header (course name, professor, date, etc.)
+  - footer with exam version number
+  - space for student name and CPF
+- The CSV must contain:
+  - exam version number
+  - correct answers for each question (letters or sum)
+4. Exam Correction
+- The system must:
+  - accept a CSV with answer keys
+  - accept a CSV with student responses
+- The system must support two correction modes:
+  - strict: any mistake results in zero for the question
+  - partial: score proportional to correct selections
+- The system must generate a grade report for the class
+---
+## Project Structure
+All system code must be inside a folder named `sistema`.
+Use the following structure:
+- sistema/backend → backend (Node.js + TypeScript)
+- sistema/frontend → frontend (React + TypeScript)
+- sistema/tests → acceptance tests (Cucumber / Gherkin)
+Keep the structure simple and organized.
+---
+We are in planning mode.
+Your goal is to design the system clearly and faithfully to these requirements.
+PHASE 1 — REQUIREMENT ANALYSIS
+- Identify ambiguities or missing details
+- Propose simple assumptions when needed
+- Do not change the original requirements
+PHASE 2 — DOMAIN DESIGN
+- Define core entities and relationships
+- Keep models simple and readable
+PHASE 3 — SYSTEM DESIGN
+- Propose a simple architecture:
+  - backend (controller, service, repository)
+  - frontend (main components)
+- Describe the main system flows
+PHASE 4 — API DESIGN
+- Define REST endpoints for each functionality
+- Keep endpoints simple and consistent
+Constraints:
+- Do not generate code
+- Follow AGENTS.md strictly
+- Prioritize simplicity and clarity
+- Avoid overengineering
+Important:
+- Stay faithful to the requirements
+- Do not invent features that are not specified
+- Do not simplify away important requirements
+Wait for my approval before implementation.</t>
+  </si>
+  <si>
+    <t>There is no straightforward or documented method to run the project locally.</t>
+  </si>
+  <si>
+    <t>Great</t>
+  </si>
+  <si>
+    <t>The prompt was well-crafted and highly effective. It consumed a lot of tokens and took a while (about 4.4M tokens).</t>
+  </si>
+  <si>
+    <t>The agent proactively asked a series of clarifying questions regarding the persistence layer, PDF generation, CSV submission, and exam versions. It then generated a logically consistent .md planning file.</t>
+  </si>
+  <si>
+    <t>Create a root-level package.json with scripts to run the backend and frontend simultaneously using concurrently. Also include a setup script to install dependencies in all subfolders (sistema/backend, sistema/frontend, sistema/tests).
+Also, create a .gitignore file at the root of the project that excludes common unnecessary files and folders.</t>
+  </si>
+  <si>
+    <t>While the project is now runnable, several problems remain: the frontend renders as a blank white screen, there are active backend errors, and some automated tests are failing.</t>
+  </si>
+  <si>
+    <t>The LLM demonstrated a clear and accurate understanding of the requirements and what needed to be accomplished.</t>
+  </si>
+  <si>
+    <t>The agent successfully set up the run scripts and .gitignore, though underlying application errors were revealed once the project booted.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md 
+The project is already implemented, but it's not working properly yet.
+I tried running it and there are several issues:
+The frontend crashes with:
+"/src/api/questions.ts does not provide an export named 'Question'"
+The backend is throwing validation errors and a lot of "FOREIGN KEY constraint failed"
+The tests are failing in multiple places:
+counts are wrong (it looks like data is not being reset between tests)
+some validations are not triggering errors when they should
+correction flow is breaking with "Body has already been read"
+some Cucumber steps are still undefined
+I don’t want a rewrite — I want you to debug and fix what’s already there.
+Focus on:
+Making backend + frontend run cleanly
+Fixing the database/state issues (especially between tests)
+Making all tests pass
+Ensuring the rules from the requirements are actually enforced
+Keep things simple and don’t add new features.
+Start by fixing backend + tests first, then frontend.
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>The frontend is still missing or failing to render, and the automated tests continue to fail.</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>It feels like the LLM is starting to lose its focus or get slightly overwhelmed by the ongoing context.</t>
+  </si>
+  <si>
+    <t>The agent shifted into planning mode, outlining a step-by-step strategy and generating a structured to-do list to systematically address the required fixes.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md 
+I was testing the system and a few issues came up that need to be fixed.
+First, there’s a frontend warning:
+"Received NaN for the value attribute"
+So somewhere we’re passing NaN to an input — that needs to be handled properly (default values or type handling).
+Also, the tests are still not all passing. Some are failing in the correction flow with:
+"Body has already been read"
+and some validations are still not behaving correctly (like invalid exam creation not returning an error).
+Before anything else, make sure:
+All tests pass
+Backend logic is correct and stable
+After that, focus on the frontend.
+Right now the frontend technically works, but it doesn’t feel like a real system:
+It’s too raw and not very pleasant to use
+The UI is too simple and looks unfinished
+I want a better UI, but still simple — clean and good-looking.
+Design direction:
+Minimalist, but visually polished
+Clean layout with good spacing
+Clear visual hierarchy (titles, sections, forms)
+Consistent structure across pages
+Use simple components (cards, forms, lists)
+Modern and good-looking (even if simple)
+Subtle use of colors and contrast (no need for anything flashy)
+Usability improvements:
+Make it obvious what the user should do on each screen
+Add small explanations or helper text where needed
+Improve feedback:
+validation errors should be clear
+success actions should be visible
+Improve flows, especially:
+creating questions
+creating exams
+correcting exams (this one is currently confusing)
+The correction screen in particular should:
+clearly explain what input is expected (CSV, format, etc.)
+show results in a structured and readable way
+Do not overengineer or add new features — just improve what already exists.
+Fix backend + tests first, then improve the frontend.
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>The correction functionality is not working as expected; the action button remains disabled (greyed out) under all conditions.</t>
+  </si>
+  <si>
+    <t>The LLM seems to be struggling with direct execution, getting bogged down in repetitive planning rather than immediately resolving the UI block.</t>
+  </si>
+  <si>
+    <t>Once again, the agent reverted to planning mode, breaking the necessary fixes down into multiple, smaller individual tasks.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+I’m still having issues with the project and I need you to focus on stabilizing it before anything else.
+First of all: the tests are still failing.
+I want you to:
+Run the tests
+Fix the issues
+Run them again
+Repeat this until ALL tests pass
+Do not stop with partial fixes — the goal is a fully passing test suite.
+From what I can see, the main problems are still around:
+Correction flow ("Body has already been read")
+Missing step definitions
+Validations not being enforced properly
+Once the backend and tests are fully working, then move to the frontend.
+Now about the system itself:
+There are some UX problems that need to be fixed:
+When creating a question, I should be able to create the alternatives at the same time (not as a separate step)
+While adding alternatives, I should be able to see the ones I’ve already added (right now it feels blind and confusing)
+The correction feature is broken:
+The button is disabled (gray) and I can’t trigger correction
+The system should support exams with mixed question types (single answer and multiple answers together)
+Frontend / UI:
+The system still feels too flat and unfinished.
+I want a UI that is:
+Minimalist, but with personality
+Good-looking and intentional (not just functional)
+Mostly black and white, with subtle accent colors
+Clean, but with character
+Design direction (important):
+Think of a very minimal, senior Japanese designer:
+very clean layouts
+strong sense of spacing
+subtle details
+slightly artistic touch
+Aesthetic reference:
+Inspired by anime like Frieren
+calm, elegant, slightly emotional, but still minimal
+So not flashy — but also not boring.
+Also improve usability:
+Make flows more intuitive
+Add small explanations where needed
+Make it clear what the user should do at each step
+Improve feedback (errors, success, empty states)
+Do not add new features beyond what is required — just fix and improve what is already there.
+Work in this order:
+Make all tests pass
+Fix backend issues
+Fix UX problems
+Improve UI
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>The automated tests are still failing and need to be prioritized.</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Highly positive. The design changes are excellent, and the previous functional bugs have been successfully resolved, though tests still need work.</t>
+  </si>
+  <si>
+    <t>The agent successfully resolved the bugs and improved the design, but failed to fix and align the automated test suite with the new code.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+The system is still not working properly and needs to be stabilized.
+First priority: tests.
+Run the test suite and keep fixing issues until ALL tests pass. Do not stop early.
+Current failing problems (be explicit and fix them one by one):
+Correction flow is broken:
+"Body has already been read" error in multiple scenarios
+Missing step definitions for result assertions
+Exam validation is incorrect:
+Creating an exam without questions is not returning an error
+Invalid answer mode is not being rejected
+Test setup is unstable:
+"fetch failed" in Before hooks (likely backend not running or reset endpoint failing)
+Question management tests are failing completely after setup breaks
+Many scenarios are being skipped because of earlier failures
+You must:
+Fix the backend so tests can run reliably
+Fix test setup (database reset / test isolation)
+Implement missing steps if needed
+If any test is incorrect or inconsistent with the requirements, fix the test
+Do this in a loop:
+run tests → fix → run again → repeat until everything passes
+After tests are passing, fix system behavior and UX:
+Problems in the system:
+The flow for creating questions and alternatives is awkward:
+I should be able to create a question and its alternatives in the same screen
+While adding alternatives, I should see the existing ones (not a blind input flow)
+There is a bug with multiple-choice questions using letters — fix this
+Corrections should be persisted:
+Corrections must be saved and linked to the exam
+One exam can have multiple corrections
+Corrections should be ordered by date
+Frontend improvements:
+Add a simple home (hello) page as the entry point
+This page should clearly offer:
+Create question
+Create exam
+Correct exam
+Improve overall flow and usability:
+Make actions more intuitive
+Add guidance text where needed
+Improve UI:
+Keep it minimal, but make it look intentional and well-designed
+Avoid a “raw” or unfinished look
+Do not add new features beyond the requirements.
+Focus on fixing, stabilizing, and improving what already exists.
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>While the major roadblocks were cleared, some minor bugs or incomplete features still remain in the project.</t>
+  </si>
+  <si>
+    <t>Positive and relieved. Although the agent didn't finish every single task, successfully fixing the tests was the most critical milestone.</t>
+  </si>
+  <si>
+    <t>The agent successfully resolved and aligned the automated tests, achieving a highly important objective, but left some peripheral tasks incomplete.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+I found some issues while using the system and I need you to fix them.
+Question creation (UI):
+When creating a question for the first time, the UI behaves strangely
+It looks like the question and alternatives are not being saved or displayed
+However, when I go to edit the question afterwards, everything appears correctly
+→ So the problem seems to be only in the initial creation flow (likely a frontend state/update issue)
+Exam correction:
+The grading logic is incorrect:
+A student who answered incorrectly received the maximum score
+Corrections are not being saved:
+After correcting an exam, the result is not linked or persisted to that exam, sort by date
+Expected behavior:
+Grading must follow the defined rules strictly
+Corrections must be saved and associated with the exam
+One exam should support multiple corrections
+UI / Design:
+The interface still feels too “test-oriented” and not like a real system
+Add more iconography to improve clarity and usability
+Keep it minimal, but give it more personality and visual structure
+Notes:
+Grading with letters seems to be working fine
+What I want:
+Fix the question creation flow
+Fix grading logic
+Fix persistence of corrections
+Improve the UI slightly (icons, clarity, structure)
+Do not rewrite the system — just fix and improve what already exists.
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>The agent did not change the UI as requested, and the exam corrections are still not linking to the exams.</t>
+  </si>
+  <si>
+    <t>Positive. It finally fixed the core issue regarding question creation.</t>
+  </si>
+  <si>
+    <t>The agent successfully fixed the question creation bug but failed to execute the requested UI changes or the correction-linking logic.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+I need a few improvements and fixes related to exams and corrections.
+---
+PDF generation flow:
+* Before generating the PDF, I want an overview screen
+* This overview should show what will be generated (exam details, questions, etc.)
+* Only after reviewing, the user should click a "Generate" button
+  → So the flow becomes: preview → then generate
+---
+Corrections:
+* Currently, corrections are not linked to exams
+* This needs to be fixed
+Expected behavior:
+* Each correction must be associated with a specific exam
+* An exam can have multiple corrections
+* short correions in the exam by date, they can also have a custom name
+---
+UI behavior:
+* In the exams list:
+  * If an exam has no corrections, it should appear visually disabled (e.g., gray)
+  * This helps indicate that no correction has been performed yet
+---
+What I want:
+* Add the PDF preview/overview step before generation
+* Fix correction persistence and linking to exams
+* Improve UI feedback in the exams list based on correction status
+Keep everything simple and consistent with the current system.
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>The exam creation screen crashes and renders as a blank white page when attempting to create a new exam.</t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>Frustrating. It appears the LLM introduced a critical UI regression causing a major blocker.</t>
+  </si>
+  <si>
+    <t>Instead of directly fixing the issue, the agent paused execution to prompt for further clarification, asking questions to resolve doubts it had.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+I found a bug when creating an exam.
+After selecting the questions and clicking to create the exam, the screen goes completely white. There’s no error shown in the terminal, so it’s likely a frontend issue (possibly a runtime error or state problem).
+What I need you to do:
+Investigate what happens when the exam is created
+Check for silent frontend errors (React rendering issues, undefined values, navigation problems, etc.)
+Fix the issue so the exam is created properly and the UI transitions correctly (e.g., redirect, success feedback, or updated list)
+Also:
+Make sure errors are not silent — if something fails, it should be visible (console or UI)
+Ensure the flow is smooth after creation (no blank screens)
+Do not rewrite the feature — just debug and fix the current implementation.
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>The system is failing to save the corrections.</t>
+  </si>
+  <si>
+    <t>Positive. It successfully solved the main white-screen bug that was blocking exam creation.</t>
+  </si>
+  <si>
+    <t>The agent successfully resolved the blank screen issue upon exam creation, but introduced a regression where corrections are no longer saving.</t>
+  </si>
+  <si>
+    <t>I want to improve the exam experience and the overall UI.
+Exam page:
+Each exam should have a button that takes me to a “corrections” view
+In this view, I should be able to see:
+the list of students
+their scores
+This should feel like a proper report, not just raw data
+PDF preview:
+The preview should be a real PDF preview, not just a simple HTML representation
+It should reflect exactly what will be generated (layout, formatting, etc.)
+UI / Design:
+The current color theme is good — do not change it
+But the UI is still too simplistic and feels a bit lifeless
+I want more personality:
+Keep it minimalist, but add character
+Small design details that make it feel intentional
+Design direction:
+Think like a senior Japanese designer
+Clean, calm, minimal — but with subtle personality
+Slight artistic touch, not just plain UI
+What I want:
+Add the corrections view for each exam
+Improve the PDF preview to be accurate and realistic
+Improve the UI to feel more polished and expressive (without overcomplicating it)</t>
+  </si>
+  <si>
+    <t>The main page crashes and renders as a completely white screen.</t>
+  </si>
+  <si>
+    <t>Frustrating, as a new critical UI regression was introduced causing a blank screen on the main landing page.</t>
+  </si>
+  <si>
+    <t>The agent failed to implement the requested UI and PDF preview improvements, breaking the main page rendering instead.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+I’m getting a critical issue in the frontend.
+The page is completely blank (white screen) when I try to use the system. There’s no visible error in the terminal, so something is failing silently on the frontend.
+What I need you to do:
+Investigate why the UI is rendering a blank page
+Check for runtime errors (React rendering issues, undefined values, bad state, routing problems, etc.)
+Look at the browser console and identify any hidden errors
+Fix it so that:
+The page renders correctly again
+The app does not fail silently
+If something goes wrong, there is at least a visible error (console or UI)
+Also:
+Make sure navigation and main flows still work after the fix
+Do not rewrite everything — just debug and fix the issue
+Explain what you found and what you changed.</t>
+  </si>
+  <si>
+    <t>The PDF loading functionality has failed and is throwing an error.</t>
+  </si>
+  <si>
+    <t>Positive. The UI changes worked, and corrections are now successfully grouped and linked to their respective exams.</t>
+  </si>
+  <si>
+    <t>The agent successfully debugged and fixed the blank screen bug on the main page.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+I found a few issues related to PDF and UI that need to be fixed.
+PDF preview:
+I’m getting this error:
+“Error Loading PDF”
+“Failed to load PDF preview”
+Fix the PDF preview so it loads correctly and consistently
+PDF layout:
+The space for the student to fill in name and CPF should be at the end of the PDF (not at the top)
+Adjust the layout accordingly while keeping it clean
+Corrections:
+Each correction should have an option to generate a PDF report
+This report should include:
+student names
+their scores
+Keep the format simple and readable
+UI:
+Remove the 📊 icon — it doesn’t fit the aesthetic
+Keep the current design direction, just make it more consistent
+What I want:
+Fix PDF preview errors
+Adjust PDF layout (name/CPF at the end)
+Add PDF export for corrections
+Clean up UI (remove inconsistent icon)</t>
+  </si>
+  <si>
+    <t>The PDF loading functionality is still failing.</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Moderate. It successfully generated the report, which was okay but still needs some refinement.</t>
+  </si>
+  <si>
+    <t>The agent successfully generated the correction report, but the core PDF loading error persists and needs further attention.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+I’m trying to render a PDF using pdf.js (pdfjs-dist), but I’m getting this error in the browser:
+"Failed to load PDF preview: Setting up fake worker failed: Failed to fetch dynamically imported module (pdf.worker.min.js from cdnjs)"
+This is likely happening because the worker is being loaded from a CDN, and the browser is blocking it.
+What I need:
+Fix the PDF rendering setup so that the worker is loaded locally (not from CDN)
+Configure pdf.js so that GlobalWorkerOptions.workerSrc points to a local file (from node_modules or a public folder)
+This must work properly with the current setup (Vite + React)
+Be explicit:
+Show the correct import statements
+Show exactly how to configure the worker
+Do not rely on external URLs
+PDF generation improvements:
+Each page of the generated exam PDF must include in the footer:
+the version number of the exam generated by the system
+The exam summary / correction PDF should:
+include student names, CPFs and grades
+present the grades in a clear table format
+What I want:
+Fix the PDF preview error properly (no hacks)
+Ensure PDF worker is correctly configured locally
+Improve generated PDFs (footer + structured grade report)
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>There is an import error causing the PDF.js worker to fail.</t>
+  </si>
+  <si>
+    <t>Disappointing. It didn't fix the main problem, making it feel like a wasted prompt.</t>
+  </si>
+  <si>
+    <t>The agent failed to correctly configure the local worker for PDF.js, leaving the Vite import error unresolved.</t>
+  </si>
+  <si>
+    <t>talp1-assignment-01 git:(master) npm run dev               
+&gt; talp1-assignment-01@1.0.0 dev
+&gt; concurrently --names "backend,frontend" --prefix-colors "cyan,magenta" "npm run dev --prefix sistema/backend" "npm run dev --prefix sistema/frontend"
+[backend] 
+[backend] &gt; backend@1.0.0 dev
+[backend] &gt; nodemon --watch src --ext ts --exec ts-node src/index.ts
+[backend] 
+[frontend] 
+[frontend] &gt; frontend@0.0.0 dev
+[frontend] &gt; vite
+[frontend] 
+[backend] [nodemon] 3.1.14
+[backend] [nodemon] to restart at any time, enter `rs`
+[backend] [nodemon] watching path(s): src/**/*
+[backend] [nodemon] watching extensions: ts
+[backend] [nodemon] starting `ts-node src/index.ts`
+[frontend] 
+[frontend]   VITE v8.0.1  ready in 120 ms
+[frontend] 
+[frontend]   ➜  Local:   http://localhost:5173/
+[frontend]   ➜  Network: use --host to expose
+[backend] Backend running on http://localhost:3001
+[frontend] 8:19:04 AM [vite] Internal server error: Failed to resolve import "pdfjs-dist/build/pdf.worker.min.js?url" from "src/components/exams/PdfPreviewViewer.tsx". Does the file exist?
+[frontend]   Plugin: vite:import-analysis
+[frontend]   File: /Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/src/components/exams/PdfPreviewViewer.tsx:4:22
+[frontend]   2  |  import * as pdfjsLib from "pdfjs-dist";
+[frontend]   3  |  // Import the worker file with ?url to get its URL for local loading
+[frontend]   4  |  import pdfWorker from "pdfjs-dist/build/pdf.worker.min.js?url";
+[frontend]      |                         ^
+[frontend]   5  |  var _jsxFileName = "/Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/src/components/exams/PdfPreviewVi...
+[frontend]   6  |  import { jsxDEV as _jsxDEV } from "react/jsx-dev-runtime";
+[frontend]       at TransformPluginContext._formatLog (file:///Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/node_modules/vite/dist/node/chunks/node.js:30234:39)
+[frontend]       at TransformPluginContext.error (file:///Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/node_modules/vite/dist/node/chunks/node.js:30231:14)
+[frontend]       at normalizeUrl (file:///Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/node_modules/vite/dist/node/chunks/node.js:27519:18)
+[frontend]       at async file:///Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/node_modules/vite/dist/node/chunks/node.js:27582:30
+[frontend]       at async Promise.all (index 2)
+[frontend]       at async TransformPluginContext.transform (file:///Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/node_modules/vite/dist/node/chunks/node.js:27550:4)
+[frontend]       at async EnvironmentPluginContainer.transform (file:///Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/node_modules/vite/dist/node/chunks/node.js:30023:14)
+[frontend]       at async loadAndTransform (file:///Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/node_modules/vite/dist/node/chunks/node.js:24152:26)
+[frontend] 8:19:04 AM [vite] (client) Pre-transform error: Failed to resolve import "pdfjs-dist/build/pdf.worker.min.js?url" from "src/components/exams/PdfPreviewViewer.tsx". Does the file exist?
+[frontend]   Plugin: vite:import-analysis
+[frontend]   File: /Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/src/components/exams/PdfPreviewViewer.tsx:4:22
+[frontend]   2  |  import * as pdfjsLib from "pdfjs-dist";
+[frontend]   3  |  // Import the worker file with ?url to get its URL for local loading
+[frontend]   4  |  import pdfWorker from "pdfjs-dist/build/pdf.worker.min.js?url";
+[frontend]      |                         ^
+[frontend]   5  |  var _jsxFileName = "/Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/src/components/exams/PdfPreviewVi...
+[frontend]   6  |  import { jsxDEV as _jsxDEV } from "react/jsx-dev-runtime";
+[frontend] 8:19:04 AM [vite] (client) Pre-transform error: Failed to resolve import "pdfjs-dist/build/pdf.worker.min.js?url" from "src/components/exams/PdfPreviewViewer.tsx". Does the file exist?
+[frontend]   Plugin: vite:import-analysis
+[frontend]   File: /Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/src/components/exams/PdfPreviewViewer.tsx:4:22
+[frontend]   2  |  import * as pdfjsLib from "pdfjs-dist";
+[frontend]   3  |  // Import the worker file with ?url to get its URL for local loading
+[frontend]   4  |  import pdfWorker from "pdfjs-dist/build/pdf.worker.min.js?url";
+[frontend]      |                         ^
+[frontend]   5  |  var _jsxFileName = "/Users/lucasreis/Documents/talp1-assignment-01/sistema/frontend/src/components/exams/PdfPreviewVi...
+[frontend]   6  |  import { jsxDEV as _jsxDEV } from "react/jsx-dev-runtime";</t>
+  </si>
+  <si>
+    <t>Failed to resolve import for the PDF worker in Vite during development, causing an internal server error.</t>
+  </si>
+  <si>
+    <t>Highly positive. It successfully sorted out the main bug with the PDF visualization.</t>
+  </si>
+  <si>
+    <t>The agent successfully debugged the Vite import error and properly configured the local PDF worker.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+I found a few issues with the PDF generation and also need a simple README.
+PDF issues:
+There is a bug where an exam that should have only one page is being generated with 3 pages:
+One page with the actual content
+One page only showing the version
+One page only showing the page number
+→ This needs to be fixed so everything is correctly placed in a single page (no extra pages)
+The PDF preview starts at 100% zoom:
+It should start at around 50% by default for better visualization
+README:
+Create a simple README for the project
+Keep it high-level and easy to understand (not too technical)
+It should include:
+What the system does
+Main flows:
+create questions
+create exams
+generate exams
+correct exams
+How to run the project (backend, frontend, tests)
+Keep it clean, short, and clear.
+What I want:
+Fix the PDF pagination/layout issue
+Adjust default zoom in the PDF preview
+Add a simple and useful README
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>The PDF generates with extra blank pages, and the default zoom level on the preview is too high.</t>
+  </si>
+  <si>
+    <t>Positive. It successfully sorted the PDF layout and formatting bugs.</t>
+  </si>
+  <si>
+    <t>The agent fixed the PDF pagination issues, adjusted the default zoom, and successfully added a clear project README.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+I want to finalize and polish the system.
+There are still a few bugs and UX/design improvements needed.
+---
+Bugs / behavior:
+* When opening an exam, the screen is completely white at first
+  * If I click zoom, it suddenly renders correctly
+    → Fix this initial rendering issue (likely related to PDF or layout not being triggered properly)
+---
+Questions:
+* Questions should be sorted by creation date (most recent first or clearly defined order)
+* Add a way to search questions by name/statement
+---
+Corrections:
+* After creating a correction, I should be able to rename it
+* Keep this simple (inline edit or small edit action)
+---
+Branding:
+* The system name should be: **Kotae**
+* On the main page, add a short explanation of what the system does
+  * Keep it subtle, smaller text, not too verbose
+---
+UI / Design:
+Right now the system works well, but it feels like it was built purely by an engineer:
+* too white
+* too flat
+* no personality
+I want to improve this.
+New direction:
+* Keep it clean and minimal
+* But add personality and warmth
+Design guidelines:
+* Use a soft pastel color palette (not just black and white)
+* Add more color, but keep it balanced and calm
+* Improve spacing and layout to feel more intentional
+* Add subtle visual elements (hover states, highlights, sections)
+Style reference:
+* A creative Japanese designer
+* Minimal, but expressive
+* Inspired by anime like Frieren:
+  * calm
+  * elegant
+  * slightly emotional
+  * not flashy, but not boring
+---
+What I want:
+* Fix the initial rendering bug
+* Improve question organization (sorting + search)
+* Allow renaming corrections
+* Add system name and small description on main page
+* Redesign UI to feel more alive, colorful, and intentional (pastel-based)
+Do not overengineer or rewrite everything — refine what already exists.
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>There is an initial white screen when opening an exam until zoom is clicked; the UI lacks personality; missing search and sorting features.</t>
+  </si>
+  <si>
+    <t>Mixed. The search bar implementation was good and the rendering bug was fixed, but the design remains too flat.</t>
+  </si>
+  <si>
+    <t>The agent fixed the rendering bug and implemented the search functionality well, but struggled to capture the requested pastel, anime-inspired aesthetic.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+A couple more improvements I’d like to make.
+Exams:
+We should be able to search exams, just like we do with questions
+This should be simple and consistent (same behavior and UX as question search)
+UI / Design:
+The design is still too flat.
+It works, but it still feels very basic and lacks visual depth and personality.
+I want you to improve the design by taking inspiration from:
+https://www.folk.app/?ref=minimal.gallery
+Focus on:
+Better visual hierarchy (clear sections, grouping of information)
+Use of cards and containers instead of everything being flat
+Subtle shadows, borders, or layers to create depth
+More intentional spacing and alignment
+A more “product-like” feel, not just a functional interface
+Keep:
+The pastel color direction
+The minimalist approach
+But:
+Add more structure and visual richness
+Make it feel like a polished product
+What I want:
+Add search for exams
+Improve UI depth and layout using the reference as inspiration
+Do not overcomplicate — just elevate the current design.
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>Missing exam search functionality and the UI still feels too flat and basic.</t>
+  </si>
+  <si>
+    <t>Moderate. The agent made subtle changes, but the overall interface is still a bit flat.</t>
+  </si>
+  <si>
+    <t>The agent successfully added the exam search, but the UI updates remained too subtle, failing to fully achieve the desired visual depth and structure.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+I want to improve stability, usability, and testing.
+Data persistence:
+Do NOT reset question or exam storage when making modifications
+Data should persist correctly across updates and operations
+Avoid any unintended resets or data loss
+Exam creation:
+When creating an exam, improve how questions are selected:
+Add a better search experience (fast and intuitive)
+Allow searching by question text/name
+Show additional context:
+Display how many correct alternatives each question has
+This helps when building exams with different types of questions
+Corrections:
+Inside an exam, in the correction flow:
+I want to be able to edit (rename) a correction
+I also want to be able to delete a correction
+Keep this simple and intuitive (inline edit or small actions)
+PDF layout:
+Each page should include:
+page number
+exam version
+The page number should appear above the version number
+Frontend tests:
+Add frontend/end-to-end tests using Selenium
+Cover key flows:
+creating questions
+creating exams
+correcting exams
+Important:
+Run the tests
+Fix issues
+Run again
+Repeat until everything passes
+Branding:
+The system name is Kotae
+Include the Japanese kanji for “Kotae” somewhere in the UI (答え)
+Keep it subtle and aligned with the design
+What I want:
+Fix persistence issues (no unwanted resets)
+Improve question selection during exam creation
+Allow editing and deleting corrections
+Adjust PDF layout (page number above version)
+Add Selenium tests and ensure they pass
+Add kanji (答え) to the branding in a tasteful way
+Do not overengineer — keep things simple and consistent.
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>The Selenium tests fail to run from the root directory and are breaking. Additionally, the PDF page numbering and versioning are broken.</t>
+  </si>
+  <si>
+    <t>Positive regarding the design. The UI changes were great, despite the new functional and testing regressions.</t>
+  </si>
+  <si>
+    <t>The agent paused execution to prompt with clarifying questions to better understand the desired outcome.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+I found a few issues that need to be fixed.
+---
+PDF generation:
+* The system is creating extra empty pages that only contain:
+  * the version number
+  * the page number
+This is incorrect.
+Expected behavior:
+* Each PDF page should contain:
+  * the actual exam content
+  * the page number
+  * the exam version
+* Do NOT generate separate or empty pages just for metadata
+---
+Correction report:
+* The generated correction report should round scores to 2 decimal places
+  * Example: 8.87 instead of long floating numbers
+---
+Frontend tests (Selenium):
+* The Selenium test suite is currently failing
+* It also does not run properly from the root using `npm test`
+What I need:
+* Fix the Selenium setup so it runs correctly from the root (`npm test`)
+* Ensure all frontend tests execute properly
+Important:
+* Run the tests
+* Fix the issues
+* Run them again
+* Repeat this process until ALL tests pass
+---
+What I want:
+* Fix PDF pagination/layout (no empty pages)
+* Fix score formatting in reports (2 decimal precision)
+* Fix Selenium setup and ensure tests run and pass from the root
+Do not overengineer — fix the root problems.
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>Tests are cleaning the current database.</t>
+  </si>
+  <si>
+    <t>Highly positive and impressed. The agent's persistence in looping to fix the tests paid off.</t>
+  </si>
+  <si>
+    <t>The agent entered a self-correction loop, repeatedly attempting fixes until the tests successfully passed. It also correctly implemented the footnote versioning in the PDFs.</t>
+  </si>
+  <si>
+    <t>@AGENTS.md
+There is a serious issue with the test setup that needs to be fixed.
+Right now, the tests are cleaning/resetting the main application database. This is not acceptable.
+Tests must be completely isolated and must NOT interfere with real data.
+What needs to be fixed:
+Tests should use a separate database (test database), not the main one
+Running tests must NOT delete or modify existing application data
+Each test run should be self-contained and reproducible
+Expected behavior:
+Use a dedicated test database (e.g., separate file or in-memory database)
+Reset ONLY the test database between scenarios
+Ensure proper isolation between tests (no shared state leaks)
+Important:
+Do not hack around this — fix the architecture properly
+The application should detect when it is running in test mode and use the correct database
+Make sure all existing tests still pass after this change
+What I want:
+Proper test isolation
+No interference with real data
+Reliable and repeatable test runs
+Explain what you changed and why.</t>
+  </si>
+  <si>
+    <t>Highly positive. The agent's proactive planning and architectural decisions were effective and much appreciated.</t>
+  </si>
+  <si>
+    <t>The agent entered planning mode to inspect potential edge cases and formulate a solution. It successfully set up a dedicated test environment, ensuring the test and development databases are now properly separated.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -51,6 +968,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
@@ -66,6 +984,19 @@
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <color rgb="FF1F1F1F"/>
+      <name val="Google Sans Text"/>
+    </font>
+    <font>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -101,7 +1032,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border/>
     <border>
       <left style="thin">
@@ -152,8 +1083,16 @@
         <color rgb="FFA5A5A5"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFA5A5A5"/>
       </right>
+      <top style="thin">
+        <color rgb="FFA5A5A5"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA5A5A5"/>
+      </left>
       <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
@@ -163,27 +1102,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFA5A5A5"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFA5A5A5"/>
+        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
         <color rgb="FFA5A5A5"/>
       </left>
-      <right style="thin">
+      <top style="thin">
         <color rgb="FFA5A5A5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
         <color rgb="FFA5A5A5"/>
@@ -199,6 +1135,28 @@
       <top style="thin">
         <color rgb="FFA5A5A5"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFA5A5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA5A5A5"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFA5A5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA5A5A5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA5A5A5"/>
+      </right>
       <bottom style="thin">
         <color rgb="FFA5A5A5"/>
       </bottom>
@@ -235,12 +1193,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -254,34 +1212,58 @@
     <xf borderId="4" fillId="3" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="3" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="7" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="13" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -572,11 +1554,21 @@
       <c r="Z2" s="4"/>
     </row>
     <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
+      <c r="A3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>10</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -600,11 +1592,21 @@
       <c r="Z3" s="4"/>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="A4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -628,11 +1630,21 @@
       <c r="Z4" s="4"/>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
+      <c r="A5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -656,11 +1668,21 @@
       <c r="Z5" s="4"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
+      <c r="A6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -684,11 +1706,21 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
+      <c r="A7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>28</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -712,11 +1744,21 @@
       <c r="Z7" s="4"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
+      <c r="A8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -740,13 +1782,21 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="13" t="s">
-        <v>6</v>
+      <c r="A9" s="9" t="s">
+        <v>33</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
+      <c r="B9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -770,11 +1820,21 @@
       <c r="Z9" s="4"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="A10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -798,11 +1858,21 @@
       <c r="Z10" s="4"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="A11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -826,11 +1896,21 @@
       <c r="Z11" s="4"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="A12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -854,11 +1934,21 @@
       <c r="Z12" s="4"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="A13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -882,11 +1972,21 @@
       <c r="Z13" s="4"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="A14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -910,11 +2010,21 @@
       <c r="Z14" s="4"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
+      <c r="A15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -938,11 +2048,21 @@
       <c r="Z15" s="4"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
+      <c r="A16" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -966,11 +2086,21 @@
       <c r="Z16" s="4"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="A17" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -994,11 +2124,21 @@
       <c r="Z17" s="4"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="A18" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -1022,11 +2162,21 @@
       <c r="Z18" s="4"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>78</v>
+      </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -1050,11 +2200,21 @@
       <c r="Z19" s="4"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>82</v>
+      </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -1078,11 +2238,21 @@
       <c r="Z20" s="4"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
+      <c r="A21" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>86</v>
+      </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -1106,11 +2276,19 @@
       <c r="Z21" s="4"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
+      <c r="A22" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>89</v>
+      </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -1134,11 +2312,11 @@
       <c r="Z22" s="4"/>
     </row>
     <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="14"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -1162,11 +2340,11 @@
       <c r="Z23" s="4"/>
     </row>
     <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -1190,11 +2368,11 @@
       <c r="Z24" s="4"/>
     </row>
     <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -1218,11 +2396,11 @@
       <c r="Z25" s="4"/>
     </row>
     <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -1246,11 +2424,11 @@
       <c r="Z26" s="4"/>
     </row>
     <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="10"/>
+      <c r="A27" s="16"/>
       <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
@@ -1274,11 +2452,11 @@
       <c r="Z27" s="4"/>
     </row>
     <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="10"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
@@ -1302,11 +2480,11 @@
       <c r="Z28" s="4"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -1330,11 +2508,11 @@
       <c r="Z29" s="4"/>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -1358,11 +2536,11 @@
       <c r="Z30" s="4"/>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -1386,11 +2564,11 @@
       <c r="Z31" s="4"/>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -1414,11 +2592,11 @@
       <c r="Z32" s="4"/>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="10"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -1442,11 +2620,11 @@
       <c r="Z33" s="4"/>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -1470,11 +2648,11 @@
       <c r="Z34" s="4"/>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -1498,11 +2676,11 @@
       <c r="Z35" s="4"/>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -1526,11 +2704,11 @@
       <c r="Z36" s="4"/>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -1554,11 +2732,11 @@
       <c r="Z37" s="4"/>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="10"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -1582,11 +2760,11 @@
       <c r="Z38" s="4"/>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="10"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -1610,11 +2788,11 @@
       <c r="Z39" s="4"/>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="10"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -1638,11 +2816,11 @@
       <c r="Z40" s="4"/>
     </row>
     <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="10"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -1666,11 +2844,11 @@
       <c r="Z41" s="4"/>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -1694,11 +2872,11 @@
       <c r="Z42" s="4"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -1722,11 +2900,11 @@
       <c r="Z43" s="4"/>
     </row>
     <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="10"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -1750,11 +2928,11 @@
       <c r="Z44" s="4"/>
     </row>
     <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -1778,11 +2956,11 @@
       <c r="Z45" s="4"/>
     </row>
     <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="14"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -1806,11 +2984,11 @@
       <c r="Z46" s="4"/>
     </row>
     <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="14"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
+      <c r="A47" s="23"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -1834,11 +3012,11 @@
       <c r="Z47" s="4"/>
     </row>
     <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="14"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
+      <c r="A48" s="23"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -1862,11 +3040,11 @@
       <c r="Z48" s="4"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="14"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -1890,11 +3068,11 @@
       <c r="Z49" s="4"/>
     </row>
     <row r="50" ht="19.5" customHeight="1">
-      <c r="A50" s="14"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
+      <c r="A50" s="23"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -1918,11 +3096,11 @@
       <c r="Z50" s="4"/>
     </row>
     <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="14"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
+      <c r="A51" s="23"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -1946,11 +3124,11 @@
       <c r="Z51" s="4"/>
     </row>
     <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="14"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
+      <c r="A52" s="23"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -1974,11 +3152,11 @@
       <c r="Z52" s="4"/>
     </row>
     <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="14"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
+      <c r="A53" s="23"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -2002,11 +3180,11 @@
       <c r="Z53" s="4"/>
     </row>
     <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="14"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
+      <c r="A54" s="23"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -2030,11 +3208,11 @@
       <c r="Z54" s="4"/>
     </row>
     <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="14"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
+      <c r="A55" s="23"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -2058,11 +3236,11 @@
       <c r="Z55" s="4"/>
     </row>
     <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="14"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -2086,11 +3264,11 @@
       <c r="Z56" s="4"/>
     </row>
     <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="14"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
+      <c r="A57" s="23"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -2114,11 +3292,11 @@
       <c r="Z57" s="4"/>
     </row>
     <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="14"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
+      <c r="A58" s="23"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -2142,11 +3320,11 @@
       <c r="Z58" s="4"/>
     </row>
     <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="14"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -2170,11 +3348,11 @@
       <c r="Z59" s="4"/>
     </row>
     <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="14"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
+      <c r="A60" s="23"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -2198,11 +3376,11 @@
       <c r="Z60" s="4"/>
     </row>
     <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="14"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
+      <c r="A61" s="23"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
@@ -2226,11 +3404,11 @@
       <c r="Z61" s="4"/>
     </row>
     <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="14"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
@@ -2254,11 +3432,11 @@
       <c r="Z62" s="4"/>
     </row>
     <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="14"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
+      <c r="A63" s="23"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
@@ -28521,12 +29699,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="A1"/>
+  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="1.0" right="1.0" top="1.0"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C000000&amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>